--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Sarmila Aadhikari</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841826609</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841826609</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -889,10 +887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +944,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L41-8</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1062,10 +1054,8 @@
           <t>Prakash Neupane</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9847329472</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9847329472</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1151,10 +1141,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1165,7 +1153,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : frquently disconnected issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1261,10 +1249,8 @@
           <t>Barsha Gurung</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9845510104</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9845510104</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1350,10 +1336,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1364,7 +1348,7 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1413,7 +1397,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1786,7 +1770,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -483,12 +483,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="31" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,22 +517,22 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1372,6 +1372,213 @@
         </is>
       </c>
       <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 9:35 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344520</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Nabindra Chaulagain</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Nabindra Chaulagain</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841295418</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:42:16 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841295418</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:42:16 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 09:35:22 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.69502</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Near Baneshwor Recreation Center,Baneshowr,Kathmandu	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>Nabindrachaulagain@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L50-4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.33543</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1425,7 +1632,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1446,7 +1653,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1736,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
@@ -1628,7 +1835,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>0</v>

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -524,7 +524,7 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -1444,10 +1444,8 @@
           <t>Nabindra Chaulagain</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841295418</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841295418</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1482,10 +1480,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.69502</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.69502</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1537,50 +1533,456 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L50-4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.33543</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.33543</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>23h 53m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>23h 53m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>23h 53m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:11 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344744</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Tirshana Ghimire</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Tirshana Ghimire</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9849459825</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:16:58 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>KLK9849459825</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:05:38 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:16:58 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>BuddhaChowk,maitrinagar kirtipur - Transportation service M7PG+JC3 Kathmandu 44618, Kathmandu, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>9851148474@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Low Optical Power</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>22h 11m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (In Progress)</t>
         </is>
       </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:09 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343059</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:09:21 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:50:55 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:09:21 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>20:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>2d 13h 18m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1595,16 +1997,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1632,7 +2034,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1642,7 +2044,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1653,7 +2055,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +2079,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>15h 6m</t>
+          <t>1d 14h 12m</t>
         </is>
       </c>
     </row>
@@ -1750,7 +2152,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1765,249 +2167,398 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Due to Optical Power flapping</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Low Optical Power</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>TKT1345199</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Sarmila Aadhikari</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : IPTV ISSUE  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>25 Sep 2026 09:32:18 AM</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>24 Sep 2026 06:26:06 PM</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>25 Sep 2026 09:32:18 AM</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>15h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343059</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:09:21 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:50:55 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:09:21 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>2d 13h 18m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1643,10 +1643,8 @@
           <t>Tirshana Ghimire</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9849459825</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9849459825</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1732,10 +1730,8 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1742,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1842,10 +1838,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1880,10 +1874,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1939,25 +1931,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2006,7 +1994,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2528,7 +2516,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -483,13 +483,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -524,12 +524,12 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="21" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1969,6 +1969,217 @@
         </is>
       </c>
       <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:39 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343489</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Indra rai</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Indra rai</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9862062974</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:39:16 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>BKT9862062974</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:43:55 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:39:16 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Nrw thimi, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>Test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>19:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 55m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -1985,7 +2196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1994,7 +2205,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2022,7 +2233,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2032,7 +2243,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2043,7 +2254,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2278,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 12m</t>
+          <t>1d 17h 26m</t>
         </is>
       </c>
     </row>
@@ -2144,10 +2355,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -2298,12 +2509,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -2321,232 +2532,322 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Low Optical Power</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Low Optical Power</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1345199</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Sarmila Aadhikari</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>25 Sep 2026 09:32:18 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 06:26:06 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>25 Sep 2026 09:32:18 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>15h 6m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>TKT1345199</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Sarmila Aadhikari</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 09:32:18 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:26:06 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 09:32:18 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>15h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>TKT1343059</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>25 Sep 2026 10:09:21 AM</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>22 Sep 2026 08:50:55 PM</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>25 Sep 2026 10:09:21 AM</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>2d 13h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343489</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Indra rai</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:39:16 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:43:55 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:39:16 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 55m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2041,10 +2041,8 @@
           <t>Indra rai</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9862062974</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9862062974</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2079,10 +2077,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2138,25 +2134,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2205,7 +2197,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2817,7 +2809,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2174,6 +2174,213 @@
       <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 12:15 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344547</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Bibhaya Paudel</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Bibhaya Paudel</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9763204623</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:49:30 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9843033061</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:57:56 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 12:15:56 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.70023</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Anamnagar, Asian Public School, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>bibhaya146@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB583</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.3296</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 26m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 18m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2432,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2246,7 +2453,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2536,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
@@ -2464,7 +2671,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2244,10 +2244,8 @@
           <t>Bibhaya Paudel</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9763204623</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9763204623</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2282,10 +2280,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.70023</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.70023</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2337,25 +2333,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>CDB583</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.3296</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.3296</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2371,6 +2371,209 @@
         </is>
       </c>
       <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 4:00 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344277</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Yogendra shrestha</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Yogendra shrestha</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9801101122</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:00:39 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9801101122</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:14:46 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:00:39 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	Imadol bhandari chowk saipatri tol, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>shrestha.yogen@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>16:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L55-8</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 45m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2387,7 +2590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2396,7 +2599,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2424,7 +2627,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2434,7 +2637,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2445,7 +2648,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2672,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 26m</t>
+          <t>1d 17h 46m</t>
         </is>
       </c>
     </row>
@@ -2528,14 +2731,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -2663,14 +2866,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -3039,6 +3242,73 @@
       <c r="M29" s="5" t="inlineStr">
         <is>
           <t>1d 23h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344277</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Yogendra shrestha</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:00:39 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:14:46 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:00:39 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 45m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2443,10 +2443,8 @@
           <t>Yogendra shrestha</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9801101122</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9801101122</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2536,10 +2534,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2550,7 +2546,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2599,7 +2595,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3278,7 +3274,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2572,6 +2572,320 @@
       <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 4:25 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>NO LIGHT IN ROUTER</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344500</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Nihongo Manabi</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Nihongo Manabi</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9860163718</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:37:02 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860163718</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:27:46 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:25:00 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>27.69910369344847, 85.23371156979962, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>9860163718@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>16:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>A01-CDB3</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 47m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 57m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2595,7 +2909,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2623,7 +2937,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2633,7 +2947,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2644,7 +2958,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2970,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6h 9m</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2982,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 46m</t>
+          <t>1d 15h 36m</t>
         </is>
       </c>
     </row>
@@ -2745,10 +3059,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -2792,107 +3106,98 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Frequent Internet Disconnection</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Due to Optical Power flapping</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +3209,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -2922,19 +3227,19 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -2945,254 +3250,158 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Low Optical Power</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Low Optical Power</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1345199</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Sarmila Aadhikari</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>25 Sep 2026 09:32:18 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>24 Sep 2026 06:26:06 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>25 Sep 2026 09:32:18 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>15h 6m</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1343059</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Saradha Panta</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>25 Sep 2026 10:09:21 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 08:50:55 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>25 Sep 2026 10:09:21 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>2d 13h 18m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1343489</t>
+          <t>TKT1345199</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Indra rai</t>
+          <t>Sarmila Aadhikari</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3212,22 +3421,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV ISSUE  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>25 Sep 2026 10:39:16 AM</t>
+          <t>25 Sep 2026 09:32:18 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>23 Sep 2026 10:43:55 AM</t>
+          <t>24 Sep 2026 06:26:06 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>25 Sep 2026 10:39:16 AM</t>
+          <t>25 Sep 2026 09:32:18 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3237,74 +3446,275 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 55m</t>
+          <t>15h 6m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>TKT1343059</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:09:21 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:50:55 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:09:21 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>2d 13h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1343489</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Indra rai</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:39:16 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:43:55 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:39:16 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>TKT1344277</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Yogendra shrestha</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>25 Sep 2026 04:00:39 PM</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>23 Sep 2026 09:14:46 PM</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>25 Sep 2026 04:00:39 PM</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>1d 18h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1344500</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Nihongo Manabi</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:37:02 AM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:27:46 AM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:25:00 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 47m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 57m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_25_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_25_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2745,10 +2745,8 @@
           <t>Nihongo Manabi</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9860163718</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9860163718</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2783,10 +2781,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2842,25 +2838,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>A01-CDB3</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -2909,7 +2901,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3684,7 +3676,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT IN ROUTER   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
